--- a/data/quotazioni/quotazioni_8ALTA.xlsx
+++ b/data/quotazioni/quotazioni_8ALTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9cb5207b7e2a247/Personale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{44F10F80-85B6-D74F-A3B3-01164D914232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDFAFB52-1CDC-1843-9D6D-F392D6E868DD}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{44F10F80-85B6-D74F-A3B3-01164D914232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92E23468-D331-CE4F-BC66-9BBBF9922040}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -813,10 +813,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -832,6 +834,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1127,6 +1133,8 @@
     <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="3"/>
+    <col min="8" max="8" width="4.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.2">
@@ -1148,7 +1156,7 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1211,13 +1219,13 @@
     </row>
     <row r="2" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>464</v>
+        <v>319</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D2" t="s">
         <v>31</v>
@@ -1228,8 +1236,8 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>18.100000000000001</v>
+      <c r="G2" s="3">
+        <v>29</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1288,36 +1296,46 @@
       <c r="Z2">
         <v>0</v>
       </c>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
+      <c r="AB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>88</v>
+        <v>472</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>27.5</v>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1376,24 +1394,16 @@
       <c r="Z3">
         <v>0</v>
       </c>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
-      <c r="AH3"/>
     </row>
     <row r="4" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>198</v>
+        <v>473</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -1404,8 +1414,8 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>32.799999999999997</v>
+      <c r="G4" s="3">
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1464,24 +1474,16 @@
       <c r="Z4">
         <v>0</v>
       </c>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-      <c r="AD4"/>
-      <c r="AE4"/>
-      <c r="AF4"/>
-      <c r="AG4"/>
-      <c r="AH4"/>
     </row>
     <row r="5" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -1492,8 +1494,8 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>42.8</v>
+      <c r="G5" s="3">
+        <v>30</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1563,13 +1565,13 @@
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -1580,8 +1582,8 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>43.3</v>
+      <c r="G6" s="3">
+        <v>28</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1640,16 +1642,24 @@
       <c r="Z6">
         <v>0</v>
       </c>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>6</v>
+        <v>467</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -1660,8 +1670,8 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>59.7</v>
+      <c r="G7" s="3">
+        <v>25</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1723,13 +1733,13 @@
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>89</v>
+        <v>294</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
@@ -1740,8 +1750,8 @@
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="G8">
-        <v>14</v>
+      <c r="G8" s="3">
+        <v>24</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1803,13 +1813,13 @@
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>121</v>
+        <v>295</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
         <v>31</v>
@@ -1820,8 +1830,8 @@
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9">
-        <v>16.399999999999999</v>
+      <c r="G9" s="3">
+        <v>25</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1883,13 +1893,13 @@
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>468</v>
+        <v>246</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -1900,8 +1910,8 @@
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10">
-        <v>18.7</v>
+      <c r="G10" s="3">
+        <v>12</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1963,13 +1973,13 @@
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>296</v>
+        <v>469</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D11" t="s">
         <v>31</v>
@@ -1980,8 +1990,8 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11">
-        <v>19.600000000000001</v>
+      <c r="G11" s="3">
+        <v>8</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2043,13 +2053,13 @@
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -2060,8 +2070,8 @@
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12">
-        <v>28.5</v>
+      <c r="G12" s="3">
+        <v>5</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2123,13 +2133,13 @@
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
         <v>31</v>
@@ -2140,8 +2150,8 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13">
-        <v>31.8</v>
+      <c r="G13" s="3">
+        <v>3</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2203,10 +2213,10 @@
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>4</v>
+        <v>293</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
         <v>241</v>
@@ -2220,8 +2230,8 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14">
-        <v>39</v>
+      <c r="G14" s="3">
+        <v>47</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2283,10 +2293,10 @@
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>293</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>241</v>
@@ -2300,8 +2310,8 @@
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="G15">
-        <v>56.9</v>
+      <c r="G15" s="3">
+        <v>49</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2363,13 +2373,13 @@
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D16" t="s">
         <v>31</v>
@@ -2380,8 +2390,8 @@
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="G16">
-        <v>1</v>
+      <c r="G16" s="3">
+        <v>29</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2441,15 +2451,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -2460,8 +2470,8 @@
       <c r="F17">
         <v>0</v>
       </c>
-      <c r="G17">
-        <v>4.7</v>
+      <c r="G17" s="3">
+        <v>24</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2521,15 +2531,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>469</v>
+        <v>296</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -2540,8 +2550,8 @@
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18">
-        <v>7.5</v>
+      <c r="G18" s="3">
+        <v>21</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2601,15 +2611,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>246</v>
+        <v>468</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
@@ -2620,8 +2630,8 @@
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19">
-        <v>8.5</v>
+      <c r="G19" s="3">
+        <v>20</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2681,15 +2691,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>295</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -2700,8 +2710,8 @@
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20">
-        <v>20.100000000000001</v>
+      <c r="G20" s="3">
+        <v>17</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2761,15 +2771,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>294</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D21" t="s">
         <v>31</v>
@@ -2780,8 +2790,8 @@
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21">
-        <v>22.4</v>
+      <c r="G21" s="3">
+        <v>14</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2841,15 +2851,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>467</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D22" t="s">
         <v>31</v>
@@ -2860,8 +2870,8 @@
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22">
-        <v>24.3</v>
+      <c r="G22" s="3">
+        <v>58</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2921,15 +2931,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D23" t="s">
         <v>31</v>
@@ -2940,8 +2950,8 @@
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23">
-        <v>27.5</v>
+      <c r="G23" s="3">
+        <v>48</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3000,24 +3010,16 @@
       <c r="Z23">
         <v>0</v>
       </c>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="1"/>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D24" t="s">
         <v>31</v>
@@ -3028,8 +3030,8 @@
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24">
-        <v>28.8</v>
+      <c r="G24" s="3">
+        <v>47</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3089,27 +3091,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>472</v>
+        <v>198</v>
       </c>
       <c r="B25" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D25" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>34</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3168,24 +3170,16 @@
       <c r="Z25">
         <v>0</v>
       </c>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
-      <c r="AG25" s="1"/>
-      <c r="AH25" s="1"/>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>473</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D26" t="s">
         <v>31</v>
@@ -3196,8 +3190,8 @@
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="G26">
-        <v>1</v>
+      <c r="G26" s="3">
+        <v>28</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3256,24 +3250,16 @@
       <c r="Z26">
         <v>0</v>
       </c>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1"/>
-      <c r="AG26" s="1"/>
-      <c r="AH26" s="1"/>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>319</v>
+        <v>464</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D27" t="s">
         <v>31</v>
@@ -3284,8 +3270,8 @@
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27">
-        <v>38.5</v>
+      <c r="G27" s="3">
+        <v>19</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -3344,36 +3330,16 @@
       <c r="Z27">
         <v>0</v>
       </c>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>209</v>
+        <v>502</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="C28" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D28" t="s">
         <v>38</v>
@@ -3384,8 +3350,8 @@
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28">
-        <v>16.2</v>
+      <c r="G28" s="3">
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -3445,15 +3411,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>252</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D29" t="s">
         <v>38</v>
@@ -3464,8 +3430,8 @@
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="G29">
-        <v>21.4</v>
+      <c r="G29" s="3">
+        <v>17</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -3525,15 +3491,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="C30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D30" t="s">
         <v>38</v>
@@ -3544,8 +3510,8 @@
       <c r="F30">
         <v>0</v>
       </c>
-      <c r="G30">
-        <v>25.9</v>
+      <c r="G30" s="3">
+        <v>1</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -3605,15 +3571,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>496</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
@@ -3624,8 +3590,8 @@
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="G31">
-        <v>28.4</v>
+      <c r="G31" s="3">
+        <v>29</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -3685,15 +3651,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>208</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
@@ -3704,8 +3670,8 @@
       <c r="F32">
         <v>0</v>
       </c>
-      <c r="G32">
-        <v>51.9</v>
+      <c r="G32" s="3">
+        <v>15</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -3767,13 +3733,13 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
@@ -3784,8 +3750,8 @@
       <c r="F33">
         <v>0</v>
       </c>
-      <c r="G33">
-        <v>4.7</v>
+      <c r="G33" s="3">
+        <v>12</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -3847,13 +3813,13 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D34" t="s">
         <v>38</v>
@@ -3864,8 +3830,8 @@
       <c r="F34">
         <v>0</v>
       </c>
-      <c r="G34">
-        <v>5.2</v>
+      <c r="G34" s="3">
+        <v>8</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3927,13 +3893,13 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>11</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D35" t="s">
         <v>38</v>
@@ -3944,8 +3910,8 @@
       <c r="F35">
         <v>0</v>
       </c>
-      <c r="G35">
-        <v>9.4</v>
+      <c r="G35" s="3">
+        <v>11</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -4007,13 +3973,13 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>504</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D36" t="s">
         <v>38</v>
@@ -4024,8 +3990,8 @@
       <c r="F36">
         <v>0</v>
       </c>
-      <c r="G36">
-        <v>11.5</v>
+      <c r="G36" s="3">
+        <v>9</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -4087,13 +4053,13 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>503</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D37" t="s">
         <v>38</v>
@@ -4104,8 +4070,8 @@
       <c r="F37">
         <v>0</v>
       </c>
-      <c r="G37">
-        <v>14.8</v>
+      <c r="G37" s="3">
+        <v>9</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -4167,13 +4133,13 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>128</v>
+        <v>1470</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>234</v>
       </c>
       <c r="C38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D38" t="s">
         <v>38</v>
@@ -4184,8 +4150,8 @@
       <c r="F38">
         <v>0</v>
       </c>
-      <c r="G38">
-        <v>16.2</v>
+      <c r="G38" s="3">
+        <v>5</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -4247,10 +4213,10 @@
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
         <v>241</v>
@@ -4264,8 +4230,8 @@
       <c r="F39">
         <v>0</v>
       </c>
-      <c r="G39">
-        <v>20.3</v>
+      <c r="G39" s="3">
+        <v>27</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4344,8 +4310,8 @@
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="G40">
-        <v>22.9</v>
+      <c r="G40" s="3">
+        <v>24</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -4407,10 +4373,10 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s">
         <v>241</v>
@@ -4424,8 +4390,8 @@
       <c r="F41">
         <v>0</v>
       </c>
-      <c r="G41">
-        <v>26.1</v>
+      <c r="G41" s="3">
+        <v>21</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -4487,13 +4453,13 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>1470</v>
+        <v>128</v>
       </c>
       <c r="B42" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D42" t="s">
         <v>38</v>
@@ -4504,8 +4470,8 @@
       <c r="F42">
         <v>0</v>
       </c>
-      <c r="G42">
-        <v>3</v>
+      <c r="G42" s="3">
+        <v>17</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -4567,13 +4533,13 @@
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D43" t="s">
         <v>38</v>
@@ -4584,8 +4550,8 @@
       <c r="F43">
         <v>0</v>
       </c>
-      <c r="G43">
-        <v>4.7</v>
+      <c r="G43" s="3">
+        <v>15</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -4647,13 +4613,13 @@
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>129</v>
+        <v>504</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D44" t="s">
         <v>38</v>
@@ -4664,8 +4630,8 @@
       <c r="F44">
         <v>0</v>
       </c>
-      <c r="G44">
-        <v>5.5</v>
+      <c r="G44" s="3">
+        <v>12</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -4727,13 +4693,13 @@
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>191</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D45" t="s">
         <v>38</v>
@@ -4744,8 +4710,8 @@
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="G45">
-        <v>6</v>
+      <c r="G45" s="3">
+        <v>21</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -4807,13 +4773,13 @@
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D46" t="s">
         <v>38</v>
@@ -4824,8 +4790,8 @@
       <c r="F46">
         <v>0</v>
       </c>
-      <c r="G46">
-        <v>7.5</v>
+      <c r="G46" s="3">
+        <v>8</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -4887,13 +4853,13 @@
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D47" t="s">
         <v>38</v>
@@ -4904,8 +4870,8 @@
       <c r="F47">
         <v>0</v>
       </c>
-      <c r="G47">
-        <v>9.3000000000000007</v>
+      <c r="G47" s="3">
+        <v>5</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -4967,13 +4933,13 @@
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>92</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D48" t="s">
         <v>38</v>
@@ -4984,8 +4950,8 @@
       <c r="F48">
         <v>0</v>
       </c>
-      <c r="G48">
-        <v>12.5</v>
+      <c r="G48" s="3">
+        <v>49</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -5047,13 +5013,13 @@
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>80</v>
+        <v>496</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="C49" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D49" t="s">
         <v>38</v>
@@ -5064,8 +5030,8 @@
       <c r="F49">
         <v>0</v>
       </c>
-      <c r="G49">
-        <v>28.1</v>
+      <c r="G49" s="3">
+        <v>29</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -5127,13 +5093,13 @@
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D50" t="s">
         <v>38</v>
@@ -5144,8 +5110,8 @@
       <c r="F50">
         <v>0</v>
       </c>
-      <c r="G50">
-        <v>1</v>
+      <c r="G50" s="3">
+        <v>26</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -5207,13 +5173,13 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>35</v>
+        <v>252</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D51" t="s">
         <v>38</v>
@@ -5224,8 +5190,8 @@
       <c r="F51">
         <v>0</v>
       </c>
-      <c r="G51">
-        <v>1.4</v>
+      <c r="G51" s="3">
+        <v>23</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -5287,13 +5253,13 @@
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>502</v>
+        <v>209</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D52" t="s">
         <v>38</v>
@@ -5304,8 +5270,8 @@
       <c r="F52">
         <v>0</v>
       </c>
-      <c r="G52">
-        <v>16</v>
+      <c r="G52" s="3">
+        <v>17</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -5367,13 +5333,13 @@
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>722</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -5384,8 +5350,8 @@
       <c r="F53">
         <v>0</v>
       </c>
-      <c r="G53">
-        <v>18.3</v>
+      <c r="G53" s="3">
+        <v>42</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -5447,13 +5413,13 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>8</v>
+        <v>727</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="C54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -5464,8 +5430,8 @@
       <c r="F54">
         <v>0</v>
       </c>
-      <c r="G54">
-        <v>34.6</v>
+      <c r="G54" s="3">
+        <v>1</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -5527,13 +5493,13 @@
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>142</v>
+        <v>728</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -5544,8 +5510,8 @@
       <c r="F55">
         <v>0</v>
       </c>
-      <c r="G55">
-        <v>35.6</v>
+      <c r="G55" s="3">
+        <v>1</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -5607,13 +5573,13 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>721</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -5624,8 +5590,8 @@
       <c r="F56">
         <v>0</v>
       </c>
-      <c r="G56">
-        <v>51.6</v>
+      <c r="G56" s="3">
+        <v>37</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -5687,13 +5653,13 @@
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="C57" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -5704,8 +5670,8 @@
       <c r="F57">
         <v>0</v>
       </c>
-      <c r="G57">
-        <v>66.099999999999994</v>
+      <c r="G57" s="3">
+        <v>32</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -5767,13 +5733,13 @@
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -5784,8 +5750,8 @@
       <c r="F58">
         <v>0</v>
       </c>
-      <c r="G58">
-        <v>99</v>
+      <c r="G58" s="3">
+        <v>31</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -5847,13 +5813,13 @@
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -5864,8 +5830,8 @@
       <c r="F59">
         <v>0</v>
       </c>
-      <c r="G59">
-        <v>101.1</v>
+      <c r="G59" s="3">
+        <v>28</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -5927,13 +5893,13 @@
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -5944,8 +5910,8 @@
       <c r="F60">
         <v>0</v>
       </c>
-      <c r="G60">
-        <v>13.1</v>
+      <c r="G60" s="3">
+        <v>25</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -6007,13 +5973,13 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>723</v>
+        <v>98</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -6024,8 +5990,8 @@
       <c r="F61">
         <v>0</v>
       </c>
-      <c r="G61">
-        <v>14.6</v>
+      <c r="G61" s="3">
+        <v>19</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -6087,13 +6053,13 @@
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D62" t="s">
         <v>27</v>
@@ -6104,8 +6070,8 @@
       <c r="F62">
         <v>0</v>
       </c>
-      <c r="G62">
-        <v>22.4</v>
+      <c r="G62" s="3">
+        <v>14</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -6167,13 +6133,13 @@
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>718</v>
+        <v>143</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D63" t="s">
         <v>27</v>
@@ -6184,8 +6150,8 @@
       <c r="F63">
         <v>0</v>
       </c>
-      <c r="G63">
-        <v>25.3</v>
+      <c r="G63" s="3">
+        <v>9</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -6247,13 +6213,13 @@
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>50</v>
+        <v>726</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D64" t="s">
         <v>27</v>
@@ -6264,8 +6230,8 @@
       <c r="F64">
         <v>0</v>
       </c>
-      <c r="G64">
-        <v>31.9</v>
+      <c r="G64" s="3">
+        <v>5</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -6327,10 +6293,10 @@
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>717</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
         <v>241</v>
@@ -6344,8 +6310,8 @@
       <c r="F65">
         <v>0</v>
       </c>
-      <c r="G65">
-        <v>35.299999999999997</v>
+      <c r="G65" s="3">
+        <v>43</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -6407,10 +6373,10 @@
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>37</v>
+        <v>717</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="C66" t="s">
         <v>241</v>
@@ -6424,8 +6390,8 @@
       <c r="F66">
         <v>0</v>
       </c>
-      <c r="G66">
-        <v>41.8</v>
+      <c r="G66" s="3">
+        <v>37</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -6487,13 +6453,13 @@
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C67" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D67" t="s">
         <v>27</v>
@@ -6504,8 +6470,8 @@
       <c r="F67">
         <v>0</v>
       </c>
-      <c r="G67">
-        <v>4.8</v>
+      <c r="G67" s="3">
+        <v>33</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -6567,13 +6533,13 @@
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D68" t="s">
         <v>27</v>
@@ -6584,8 +6550,8 @@
       <c r="F68">
         <v>0</v>
       </c>
-      <c r="G68">
-        <v>4.8</v>
+      <c r="G68" s="3">
+        <v>26</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -6647,13 +6613,13 @@
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D69" t="s">
         <v>27</v>
@@ -6664,8 +6630,8 @@
       <c r="F69">
         <v>0</v>
       </c>
-      <c r="G69">
-        <v>9.5</v>
+      <c r="G69" s="3">
+        <v>24</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -6727,13 +6693,13 @@
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>98</v>
+        <v>723</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D70" t="s">
         <v>27</v>
@@ -6744,8 +6710,8 @@
       <c r="F70">
         <v>0</v>
       </c>
-      <c r="G70">
-        <v>11</v>
+      <c r="G70" s="3">
+        <v>15</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -6807,13 +6773,13 @@
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C71" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D71" t="s">
         <v>27</v>
@@ -6824,8 +6790,8 @@
       <c r="F71">
         <v>0</v>
       </c>
-      <c r="G71">
-        <v>24.3</v>
+      <c r="G71" s="3">
+        <v>13</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -6887,13 +6853,13 @@
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D72" t="s">
         <v>27</v>
@@ -6904,8 +6870,8 @@
       <c r="F72">
         <v>0</v>
       </c>
-      <c r="G72">
-        <v>27.1</v>
+      <c r="G72" s="3">
+        <v>105</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -6967,13 +6933,13 @@
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C73" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D73" t="s">
         <v>27</v>
@@ -6984,8 +6950,8 @@
       <c r="F73">
         <v>0</v>
       </c>
-      <c r="G73">
-        <v>30.3</v>
+      <c r="G73" s="3">
+        <v>95</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -7047,13 +7013,13 @@
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C74" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D74" t="s">
         <v>27</v>
@@ -7064,8 +7030,8 @@
       <c r="F74">
         <v>0</v>
       </c>
-      <c r="G74">
-        <v>31.1</v>
+      <c r="G74" s="3">
+        <v>83</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -7127,13 +7093,13 @@
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>141</v>
+        <v>721</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="C75" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D75" t="s">
         <v>27</v>
@@ -7144,8 +7110,8 @@
       <c r="F75">
         <v>0</v>
       </c>
-      <c r="G75">
-        <v>35.1</v>
+      <c r="G75" s="3">
+        <v>42</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -7207,13 +7173,13 @@
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>727</v>
+        <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="C76" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D76" t="s">
         <v>27</v>
@@ -7224,8 +7190,8 @@
       <c r="F76">
         <v>0</v>
       </c>
-      <c r="G76">
-        <v>1</v>
+      <c r="G76" s="3">
+        <v>37</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -7287,13 +7253,13 @@
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>728</v>
+        <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="C77" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D77" t="s">
         <v>27</v>
@@ -7304,8 +7270,8 @@
       <c r="F77">
         <v>0</v>
       </c>
-      <c r="G77">
-        <v>1</v>
+      <c r="G77" s="3">
+        <v>45</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -7367,13 +7333,13 @@
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>49</v>
+        <v>722</v>
       </c>
       <c r="B78" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="C78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D78" t="s">
         <v>27</v>
@@ -7384,8 +7350,8 @@
       <c r="F78">
         <v>0</v>
       </c>
-      <c r="G78">
-        <v>39.700000000000003</v>
+      <c r="G78" s="3">
+        <v>19</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -7447,13 +7413,13 @@
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>1445</v>
+        <v>269</v>
       </c>
       <c r="B79" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="C79" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D79" t="s">
         <v>43</v>
@@ -7464,8 +7430,8 @@
       <c r="F79">
         <v>0</v>
       </c>
-      <c r="G79">
-        <v>2</v>
+      <c r="G79" s="3">
+        <v>26</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -7527,13 +7493,13 @@
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>1554</v>
+        <v>1442</v>
       </c>
       <c r="B80" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C80" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D80" t="s">
         <v>43</v>
@@ -7544,8 +7510,8 @@
       <c r="F80">
         <v>0</v>
       </c>
-      <c r="G80">
-        <v>4.7</v>
+      <c r="G80" s="3">
+        <v>1</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -7607,13 +7573,13 @@
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>40</v>
+        <v>1443</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>229</v>
       </c>
       <c r="C81" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D81" t="s">
         <v>43</v>
@@ -7624,8 +7590,8 @@
       <c r="F81">
         <v>0</v>
       </c>
-      <c r="G81">
-        <v>14.6</v>
+      <c r="G81" s="3">
+        <v>1</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -7687,13 +7653,13 @@
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D82" t="s">
         <v>43</v>
@@ -7704,8 +7670,8 @@
       <c r="F82">
         <v>0</v>
       </c>
-      <c r="G82">
-        <v>21.3</v>
+      <c r="G82" s="3">
+        <v>43</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -7767,13 +7733,13 @@
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C83" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D83" t="s">
         <v>43</v>
@@ -7784,8 +7750,8 @@
       <c r="F83">
         <v>0</v>
       </c>
-      <c r="G83">
-        <v>21.7</v>
+      <c r="G83" s="3">
+        <v>21</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -7847,13 +7813,13 @@
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>936</v>
+        <v>154</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="C84" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D84" t="s">
         <v>43</v>
@@ -7864,8 +7830,8 @@
       <c r="F84">
         <v>0</v>
       </c>
-      <c r="G84">
-        <v>24.4</v>
+      <c r="G84" s="3">
+        <v>21</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -7927,13 +7893,13 @@
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="B85" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C85" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D85" t="s">
         <v>43</v>
@@ -7944,8 +7910,8 @@
       <c r="F85">
         <v>0</v>
       </c>
-      <c r="G85">
-        <v>5.2</v>
+      <c r="G85" s="3">
+        <v>17</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -8007,13 +7973,13 @@
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>156</v>
+        <v>1526</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>238</v>
       </c>
       <c r="C86" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D86" t="s">
         <v>43</v>
@@ -8024,8 +7990,8 @@
       <c r="F86">
         <v>0</v>
       </c>
-      <c r="G86">
-        <v>9.6</v>
+      <c r="G86" s="3">
+        <v>3</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -8087,13 +8053,13 @@
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>1446</v>
+        <v>21</v>
       </c>
       <c r="B87" t="s">
-        <v>231</v>
+        <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D87" t="s">
         <v>43</v>
@@ -8104,8 +8070,8 @@
       <c r="F87">
         <v>0</v>
       </c>
-      <c r="G87">
-        <v>16</v>
+      <c r="G87" s="3">
+        <v>22</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -8167,13 +8133,13 @@
     </row>
     <row r="88" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>39</v>
+        <v>943</v>
       </c>
       <c r="B88" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D88" t="s">
         <v>43</v>
@@ -8184,8 +8150,8 @@
       <c r="F88">
         <v>0</v>
       </c>
-      <c r="G88">
-        <v>20.9</v>
+      <c r="G88" s="3">
+        <v>2</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -8247,13 +8213,13 @@
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>54</v>
+        <v>1555</v>
       </c>
       <c r="B89" t="s">
-        <v>59</v>
+        <v>240</v>
       </c>
       <c r="C89" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D89" t="s">
         <v>43</v>
@@ -8264,8 +8230,8 @@
       <c r="F89">
         <v>0</v>
       </c>
-      <c r="G89">
-        <v>22.9</v>
+      <c r="G89" s="3">
+        <v>2</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -8327,13 +8293,13 @@
     </row>
     <row r="90" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>153</v>
+        <v>941</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="C90" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D90" t="s">
         <v>43</v>
@@ -8344,8 +8310,8 @@
       <c r="F90">
         <v>0</v>
       </c>
-      <c r="G90">
-        <v>24.7</v>
+      <c r="G90" s="3">
+        <v>1</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -8424,8 +8390,8 @@
       <c r="F91">
         <v>0</v>
       </c>
-      <c r="G91">
-        <v>34.4</v>
+      <c r="G91" s="3">
+        <v>61</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -8504,8 +8470,8 @@
       <c r="F92">
         <v>0</v>
       </c>
-      <c r="G92">
-        <v>34.4</v>
+      <c r="G92" s="3">
+        <v>42</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -8567,13 +8533,13 @@
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>941</v>
+        <v>153</v>
       </c>
       <c r="B93" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="C93" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D93" t="s">
         <v>43</v>
@@ -8584,8 +8550,8 @@
       <c r="F93">
         <v>0</v>
       </c>
-      <c r="G93">
-        <v>1</v>
+      <c r="G93" s="3">
+        <v>25</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -8647,13 +8613,13 @@
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>943</v>
+        <v>54</v>
       </c>
       <c r="B94" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="C94" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D94" t="s">
         <v>43</v>
@@ -8664,8 +8630,8 @@
       <c r="F94">
         <v>0</v>
       </c>
-      <c r="G94">
-        <v>2</v>
+      <c r="G94" s="3">
+        <v>24</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -8727,13 +8693,13 @@
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>1555</v>
+        <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>240</v>
+        <v>51</v>
       </c>
       <c r="C95" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D95" t="s">
         <v>43</v>
@@ -8744,8 +8710,8 @@
       <c r="F95">
         <v>0</v>
       </c>
-      <c r="G95">
-        <v>2</v>
+      <c r="G95" s="3">
+        <v>22</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -8807,13 +8773,13 @@
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>21</v>
+        <v>1446</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="C96" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D96" t="s">
         <v>43</v>
@@ -8824,8 +8790,8 @@
       <c r="F96">
         <v>0</v>
       </c>
-      <c r="G96">
-        <v>2.9</v>
+      <c r="G96" s="3">
+        <v>17</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -8887,13 +8853,13 @@
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>1526</v>
+        <v>156</v>
       </c>
       <c r="B97" t="s">
-        <v>238</v>
+        <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D97" t="s">
         <v>43</v>
@@ -8904,8 +8870,8 @@
       <c r="F97">
         <v>0</v>
       </c>
-      <c r="G97">
-        <v>3</v>
+      <c r="G97" s="3">
+        <v>10</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -8967,13 +8933,13 @@
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D98" t="s">
         <v>43</v>
@@ -8984,8 +8950,8 @@
       <c r="F98">
         <v>0</v>
       </c>
-      <c r="G98">
-        <v>13.3</v>
+      <c r="G98" s="3">
+        <v>11</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -9047,13 +9013,13 @@
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>154</v>
+        <v>936</v>
       </c>
       <c r="B99" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="C99" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D99" t="s">
         <v>43</v>
@@ -9064,8 +9030,8 @@
       <c r="F99">
         <v>0</v>
       </c>
-      <c r="G99">
-        <v>18.2</v>
+      <c r="G99" s="3">
+        <v>25</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -9127,13 +9093,13 @@
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B100" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C100" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D100" t="s">
         <v>43</v>
@@ -9144,8 +9110,8 @@
       <c r="F100">
         <v>0</v>
       </c>
-      <c r="G100">
-        <v>18.3</v>
+      <c r="G100" s="3">
+        <v>23</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -9207,13 +9173,13 @@
     </row>
     <row r="101" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C101" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D101" t="s">
         <v>43</v>
@@ -9224,8 +9190,8 @@
       <c r="F101">
         <v>0</v>
       </c>
-      <c r="G101">
-        <v>41.7</v>
+      <c r="G101" s="3">
+        <v>22</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -9287,13 +9253,13 @@
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>1442</v>
+        <v>40</v>
       </c>
       <c r="B102" t="s">
-        <v>228</v>
+        <v>52</v>
       </c>
       <c r="C102" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D102" t="s">
         <v>43</v>
@@ -9304,8 +9270,8 @@
       <c r="F102">
         <v>0</v>
       </c>
-      <c r="G102">
-        <v>1</v>
+      <c r="G102" s="3">
+        <v>15</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -9367,13 +9333,13 @@
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>1443</v>
+        <v>1554</v>
       </c>
       <c r="B103" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C103" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D103" t="s">
         <v>43</v>
@@ -9384,8 +9350,8 @@
       <c r="F103">
         <v>0</v>
       </c>
-      <c r="G103">
-        <v>1</v>
+      <c r="G103" s="3">
+        <v>5</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -9447,13 +9413,13 @@
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>269</v>
+        <v>1445</v>
       </c>
       <c r="B104" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="C104" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D104" t="s">
         <v>43</v>
@@ -9464,8 +9430,8 @@
       <c r="F104">
         <v>0</v>
       </c>
-      <c r="G104">
-        <v>20.7</v>
+      <c r="G104" s="3">
+        <v>2</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -9527,13 +9493,13 @@
     </row>
     <row r="105" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="C105" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
@@ -9544,8 +9510,8 @@
       <c r="F105">
         <v>0</v>
       </c>
-      <c r="G105">
-        <v>1.9</v>
+      <c r="G105" s="3">
+        <v>7</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -9607,13 +9573,13 @@
     </row>
     <row r="106" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>168</v>
+        <v>1047</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="C106" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D106" t="s">
         <v>41</v>
@@ -9624,8 +9590,8 @@
       <c r="F106">
         <v>0</v>
       </c>
-      <c r="G106">
-        <v>8.5</v>
+      <c r="G106" s="3">
+        <v>1</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -9687,13 +9653,13 @@
     </row>
     <row r="107" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>1504</v>
+        <v>1048</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="C107" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D107" t="s">
         <v>41</v>
@@ -9704,8 +9670,8 @@
       <c r="F107">
         <v>0</v>
       </c>
-      <c r="G107">
-        <v>9.1</v>
+      <c r="G107" s="3">
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -9767,13 +9733,13 @@
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>1044</v>
+        <v>31</v>
       </c>
       <c r="B108" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C108" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D108" t="s">
         <v>41</v>
@@ -9784,8 +9750,8 @@
       <c r="F108">
         <v>0</v>
       </c>
-      <c r="G108">
-        <v>10.5</v>
+      <c r="G108" s="3">
+        <v>16</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -9847,13 +9813,13 @@
     </row>
     <row r="109" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="B109" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="C109" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D109" t="s">
         <v>41</v>
@@ -9864,8 +9830,8 @@
       <c r="F109">
         <v>0</v>
       </c>
-      <c r="G109">
-        <v>11.4</v>
+      <c r="G109" s="3">
+        <v>16</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -9927,13 +9893,13 @@
     </row>
     <row r="110" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="B110" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C110" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D110" t="s">
         <v>41</v>
@@ -9944,8 +9910,8 @@
       <c r="F110">
         <v>0</v>
       </c>
-      <c r="G110">
-        <v>11.5</v>
+      <c r="G110" s="3">
+        <v>14</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -10007,13 +9973,13 @@
     </row>
     <row r="111" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>277</v>
+        <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D111" t="s">
         <v>41</v>
@@ -10024,8 +9990,8 @@
       <c r="F111">
         <v>0</v>
       </c>
-      <c r="G111">
-        <v>14.4</v>
+      <c r="G111" s="3">
+        <v>12</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -10087,13 +10053,13 @@
     </row>
     <row r="112" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="B112" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="C112" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D112" t="s">
         <v>41</v>
@@ -10104,8 +10070,8 @@
       <c r="F112">
         <v>0</v>
       </c>
-      <c r="G112">
-        <v>2</v>
+      <c r="G112" s="3">
+        <v>12</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -10167,13 +10133,13 @@
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="C113" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D113" t="s">
         <v>41</v>
@@ -10184,8 +10150,8 @@
       <c r="F113">
         <v>0</v>
       </c>
-      <c r="G113">
-        <v>5.2</v>
+      <c r="G113" s="3">
+        <v>11</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -10247,13 +10213,13 @@
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="B114" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="C114" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D114" t="s">
         <v>41</v>
@@ -10264,8 +10230,8 @@
       <c r="F114">
         <v>0</v>
       </c>
-      <c r="G114">
-        <v>7.2</v>
+      <c r="G114" s="3">
+        <v>8</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -10327,10 +10293,10 @@
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>1042</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="C115" t="s">
         <v>241</v>
@@ -10344,8 +10310,8 @@
       <c r="F115">
         <v>0</v>
       </c>
-      <c r="G115">
-        <v>10.6</v>
+      <c r="G115" s="3">
+        <v>20</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -10407,10 +10373,10 @@
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>1039</v>
+        <v>58</v>
       </c>
       <c r="B116" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="C116" t="s">
         <v>241</v>
@@ -10424,8 +10390,8 @@
       <c r="F116">
         <v>0</v>
       </c>
-      <c r="G116">
-        <v>12</v>
+      <c r="G116" s="3">
+        <v>16</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -10504,8 +10470,8 @@
       <c r="F117">
         <v>0</v>
       </c>
-      <c r="G117">
-        <v>12.4</v>
+      <c r="G117" s="3">
+        <v>13</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -10567,10 +10533,10 @@
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A118">
-        <v>58</v>
+        <v>1039</v>
       </c>
       <c r="B118" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="C118" t="s">
         <v>241</v>
@@ -10584,8 +10550,8 @@
       <c r="F118">
         <v>0</v>
       </c>
-      <c r="G118">
-        <v>15</v>
+      <c r="G118" s="3">
+        <v>12</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -10647,10 +10613,10 @@
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>17</v>
+        <v>1042</v>
       </c>
       <c r="B119" t="s">
-        <v>40</v>
+        <v>172</v>
       </c>
       <c r="C119" t="s">
         <v>241</v>
@@ -10664,8 +10630,8 @@
       <c r="F119">
         <v>0</v>
       </c>
-      <c r="G119">
-        <v>19.2</v>
+      <c r="G119" s="3">
+        <v>11</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -10727,13 +10693,13 @@
     </row>
     <row r="120" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>276</v>
+        <v>113</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="C120" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D120" t="s">
         <v>41</v>
@@ -10744,8 +10710,8 @@
       <c r="F120">
         <v>0</v>
       </c>
-      <c r="G120">
-        <v>8.5</v>
+      <c r="G120" s="3">
+        <v>11</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -10807,13 +10773,13 @@
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A121">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="B121" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C121" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D121" t="s">
         <v>41</v>
@@ -10824,8 +10790,8 @@
       <c r="F121">
         <v>0</v>
       </c>
-      <c r="G121">
-        <v>11</v>
+      <c r="G121" s="3">
+        <v>6</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -10887,13 +10853,13 @@
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="B122" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C122" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D122" t="s">
         <v>41</v>
@@ -10904,8 +10870,8 @@
       <c r="F122">
         <v>0</v>
       </c>
-      <c r="G122">
-        <v>11.4</v>
+      <c r="G122" s="3">
+        <v>2</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -10967,13 +10933,13 @@
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>112</v>
+        <v>277</v>
       </c>
       <c r="B123" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="C123" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D123" t="s">
         <v>41</v>
@@ -10984,8 +10950,8 @@
       <c r="F123">
         <v>0</v>
       </c>
-      <c r="G123">
-        <v>11.8</v>
+      <c r="G123" s="3">
+        <v>15</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -11047,13 +11013,13 @@
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="B124" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C124" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D124" t="s">
         <v>41</v>
@@ -11064,8 +11030,8 @@
       <c r="F124">
         <v>0</v>
       </c>
-      <c r="G124">
-        <v>13.6</v>
+      <c r="G124" s="3">
+        <v>12</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -11127,13 +11093,13 @@
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="B125" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C125" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D125" t="s">
         <v>41</v>
@@ -11144,8 +11110,8 @@
       <c r="F125">
         <v>0</v>
       </c>
-      <c r="G125">
-        <v>15</v>
+      <c r="G125" s="3">
+        <v>12</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -11207,13 +11173,13 @@
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>232</v>
+        <v>1044</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="C126" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D126" t="s">
         <v>41</v>
@@ -11224,8 +11190,8 @@
       <c r="F126">
         <v>0</v>
       </c>
-      <c r="G126">
-        <v>15</v>
+      <c r="G126" s="3">
+        <v>11</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -11287,13 +11253,13 @@
     </row>
     <row r="127" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>1047</v>
+        <v>1504</v>
       </c>
       <c r="B127" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D127" t="s">
         <v>41</v>
@@ -11304,8 +11270,8 @@
       <c r="F127">
         <v>0</v>
       </c>
-      <c r="G127">
-        <v>1</v>
+      <c r="G127" s="3">
+        <v>9</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -11367,13 +11333,13 @@
     </row>
     <row r="128" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>1048</v>
+        <v>168</v>
       </c>
       <c r="B128" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="C128" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D128" t="s">
         <v>41</v>
@@ -11384,8 +11350,8 @@
       <c r="F128">
         <v>0</v>
       </c>
-      <c r="G128">
-        <v>1</v>
+      <c r="G128" s="3">
+        <v>8</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -11447,13 +11413,13 @@
     </row>
     <row r="129" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>60</v>
+        <v>1045</v>
       </c>
       <c r="B129" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="C129" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D129" t="s">
         <v>41</v>
@@ -11464,8 +11430,8 @@
       <c r="F129">
         <v>0</v>
       </c>
-      <c r="G129">
-        <v>6.8</v>
+      <c r="G129" s="3">
+        <v>5</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -11527,10 +11493,10 @@
     </row>
     <row r="130" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>1045</v>
+        <v>169</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="C130" t="s">
         <v>242</v>
@@ -11544,8 +11510,8 @@
       <c r="F130">
         <v>0</v>
       </c>
-      <c r="G130">
-        <v>4.7</v>
+      <c r="G130" s="3">
+        <v>2</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -11607,13 +11573,13 @@
     </row>
     <row r="131" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="B131" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D131" t="s">
         <v>179</v>
@@ -11624,8 +11590,8 @@
       <c r="F131">
         <v>0</v>
       </c>
-      <c r="G131">
-        <v>19</v>
+      <c r="G131" s="3">
+        <v>34</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -11687,13 +11653,13 @@
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B132" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C132" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D132" t="s">
         <v>179</v>
@@ -11704,8 +11670,8 @@
       <c r="F132">
         <v>0</v>
       </c>
-      <c r="G132">
-        <v>22.5</v>
+      <c r="G132" s="3">
+        <v>1</v>
       </c>
       <c r="H132">
         <v>0</v>
@@ -11767,13 +11733,13 @@
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="B133" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C133" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D133" t="s">
         <v>179</v>
@@ -11784,8 +11750,8 @@
       <c r="F133">
         <v>0</v>
       </c>
-      <c r="G133">
-        <v>36.700000000000003</v>
+      <c r="G133" s="3">
+        <v>1</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -11847,13 +11813,13 @@
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>1068</v>
+        <v>1052</v>
       </c>
       <c r="B134" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C134" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D134" t="s">
         <v>179</v>
@@ -11864,8 +11830,8 @@
       <c r="F134">
         <v>0</v>
       </c>
-      <c r="G134">
-        <v>37.5</v>
+      <c r="G134" s="3">
+        <v>43</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -11927,13 +11893,13 @@
     </row>
     <row r="135" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>1067</v>
+        <v>1053</v>
       </c>
       <c r="B135" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C135" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D135" t="s">
         <v>179</v>
@@ -11944,8 +11910,8 @@
       <c r="F135">
         <v>0</v>
       </c>
-      <c r="G135">
-        <v>39.5</v>
+      <c r="G135" s="3">
+        <v>36</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -12007,13 +11973,13 @@
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="B136" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C136" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D136" t="s">
         <v>179</v>
@@ -12024,8 +11990,8 @@
       <c r="F136">
         <v>0</v>
       </c>
-      <c r="G136">
-        <v>48.8</v>
+      <c r="G136" s="3">
+        <v>35</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -12087,13 +12053,13 @@
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>1065</v>
+        <v>1057</v>
       </c>
       <c r="B137" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C137" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D137" t="s">
         <v>179</v>
@@ -12104,8 +12070,8 @@
       <c r="F137">
         <v>0</v>
       </c>
-      <c r="G137">
-        <v>80.5</v>
+      <c r="G137" s="3">
+        <v>27</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -12167,13 +12133,13 @@
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B138" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C138" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D138" t="s">
         <v>179</v>
@@ -12184,8 +12150,8 @@
       <c r="F138">
         <v>0</v>
       </c>
-      <c r="G138">
-        <v>13.4</v>
+      <c r="G138" s="3">
+        <v>15</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -12247,13 +12213,13 @@
     </row>
     <row r="139" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>1060</v>
+        <v>1523</v>
       </c>
       <c r="B139" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="C139" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D139" t="s">
         <v>179</v>
@@ -12264,8 +12230,8 @@
       <c r="F139">
         <v>0</v>
       </c>
-      <c r="G139">
-        <v>17.2</v>
+      <c r="G139" s="3">
+        <v>11</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -12327,13 +12293,13 @@
     </row>
     <row r="140" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="B140" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C140" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D140" t="s">
         <v>179</v>
@@ -12344,8 +12310,8 @@
       <c r="F140">
         <v>0</v>
       </c>
-      <c r="G140">
-        <v>19.3</v>
+      <c r="G140" s="3">
+        <v>20</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -12407,13 +12373,13 @@
     </row>
     <row r="141" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>1055</v>
+        <v>1064</v>
       </c>
       <c r="B141" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C141" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D141" t="s">
         <v>179</v>
@@ -12424,8 +12390,8 @@
       <c r="F141">
         <v>0</v>
       </c>
-      <c r="G141">
-        <v>37.200000000000003</v>
+      <c r="G141" s="3">
+        <v>7</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -12487,10 +12453,10 @@
     </row>
     <row r="142" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B142" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C142" t="s">
         <v>241</v>
@@ -12504,8 +12470,8 @@
       <c r="F142">
         <v>0</v>
       </c>
-      <c r="G142">
-        <v>41.8</v>
+      <c r="G142" s="3">
+        <v>55</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -12584,8 +12550,8 @@
       <c r="F143">
         <v>0</v>
       </c>
-      <c r="G143">
-        <v>50.3</v>
+      <c r="G143" s="3">
+        <v>47</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -12647,10 +12613,10 @@
     </row>
     <row r="144" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B144" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C144" t="s">
         <v>241</v>
@@ -12664,8 +12630,8 @@
       <c r="F144">
         <v>0</v>
       </c>
-      <c r="G144">
-        <v>56.1</v>
+      <c r="G144" s="3">
+        <v>46</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -12727,13 +12693,13 @@
     </row>
     <row r="145" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>1064</v>
+        <v>1055</v>
       </c>
       <c r="B145" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C145" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D145" t="s">
         <v>179</v>
@@ -12744,8 +12710,8 @@
       <c r="F145">
         <v>0</v>
       </c>
-      <c r="G145">
-        <v>6.7</v>
+      <c r="G145" s="3">
+        <v>39</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -12807,13 +12773,13 @@
     </row>
     <row r="146" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>1072</v>
+        <v>1059</v>
       </c>
       <c r="B146" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C146" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D146" t="s">
         <v>179</v>
@@ -12824,8 +12790,8 @@
       <c r="F146">
         <v>0</v>
       </c>
-      <c r="G146">
-        <v>7.1</v>
+      <c r="G146" s="3">
+        <v>20</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -12887,13 +12853,13 @@
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>1523</v>
+        <v>1060</v>
       </c>
       <c r="B147" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="C147" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D147" t="s">
         <v>179</v>
@@ -12904,8 +12870,8 @@
       <c r="F147">
         <v>0</v>
       </c>
-      <c r="G147">
-        <v>11</v>
+      <c r="G147" s="3">
+        <v>18</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -12967,13 +12933,13 @@
     </row>
     <row r="148" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B148" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C148" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D148" t="s">
         <v>179</v>
@@ -12984,8 +12950,8 @@
       <c r="F148">
         <v>0</v>
       </c>
-      <c r="G148">
-        <v>14.6</v>
+      <c r="G148" s="3">
+        <v>14</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -13047,13 +13013,13 @@
     </row>
     <row r="149" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B149" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C149" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D149" t="s">
         <v>179</v>
@@ -13064,8 +13030,8 @@
       <c r="F149">
         <v>0</v>
       </c>
-      <c r="G149">
-        <v>26.2</v>
+      <c r="G149" s="3">
+        <v>11</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -13127,13 +13093,13 @@
     </row>
     <row r="150" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="B150" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C150" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D150" t="s">
         <v>179</v>
@@ -13144,8 +13110,8 @@
       <c r="F150">
         <v>0</v>
       </c>
-      <c r="G150">
-        <v>33.9</v>
+      <c r="G150" s="3">
+        <v>75</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -13207,13 +13173,13 @@
     </row>
     <row r="151" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>1053</v>
+        <v>1066</v>
       </c>
       <c r="B151" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C151" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D151" t="s">
         <v>179</v>
@@ -13224,8 +13190,8 @@
       <c r="F151">
         <v>0</v>
       </c>
-      <c r="G151">
-        <v>34.4</v>
+      <c r="G151" s="3">
+        <v>51</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -13287,13 +13253,13 @@
     </row>
     <row r="152" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>1052</v>
+        <v>1067</v>
       </c>
       <c r="B152" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C152" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D152" t="s">
         <v>179</v>
@@ -13304,8 +13270,8 @@
       <c r="F152">
         <v>0</v>
       </c>
-      <c r="G152">
-        <v>41.4</v>
+      <c r="G152" s="3">
+        <v>41</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -13367,13 +13333,13 @@
     </row>
     <row r="153" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="B153" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D153" t="s">
         <v>179</v>
@@ -13384,8 +13350,8 @@
       <c r="F153">
         <v>0</v>
       </c>
-      <c r="G153">
-        <v>1</v>
+      <c r="G153" s="3">
+        <v>58</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -13447,13 +13413,13 @@
     </row>
     <row r="154" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="B154" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C154" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D154" t="s">
         <v>179</v>
@@ -13464,8 +13430,8 @@
       <c r="F154">
         <v>0</v>
       </c>
-      <c r="G154">
-        <v>1</v>
+      <c r="G154" s="3">
+        <v>38</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -13527,13 +13493,13 @@
     </row>
     <row r="155" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>1056</v>
+        <v>1070</v>
       </c>
       <c r="B155" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C155" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D155" t="s">
         <v>179</v>
@@ -13544,8 +13510,8 @@
       <c r="F155">
         <v>0</v>
       </c>
-      <c r="G155">
-        <v>36</v>
+      <c r="G155" s="3">
+        <v>24</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -13607,13 +13573,13 @@
     </row>
     <row r="156" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="B156" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C156" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D156" t="s">
         <v>179</v>
@@ -13624,8 +13590,8 @@
       <c r="F156">
         <v>0</v>
       </c>
-      <c r="G156">
-        <v>10.8</v>
+      <c r="G156" s="3">
+        <v>32</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -13687,13 +13653,13 @@
     </row>
     <row r="157" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>1195</v>
+        <v>67</v>
       </c>
       <c r="B157" t="s">
-        <v>209</v>
+        <v>65</v>
       </c>
       <c r="C157" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D157" t="s">
         <v>29</v>
@@ -13704,8 +13670,8 @@
       <c r="F157">
         <v>0</v>
       </c>
-      <c r="G157">
-        <v>15</v>
+      <c r="G157" s="3">
+        <v>39</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -13767,13 +13733,13 @@
     </row>
     <row r="158" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>1441</v>
+        <v>1196</v>
       </c>
       <c r="B158" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="C158" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D158" t="s">
         <v>29</v>
@@ -13784,8 +13750,8 @@
       <c r="F158">
         <v>0</v>
       </c>
-      <c r="G158">
-        <v>46.4</v>
+      <c r="G158" s="3">
+        <v>1</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -13847,13 +13813,13 @@
     </row>
     <row r="159" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>3</v>
+        <v>1198</v>
       </c>
       <c r="B159" t="s">
-        <v>28</v>
+        <v>211</v>
       </c>
       <c r="C159" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D159" t="s">
         <v>29</v>
@@ -13864,8 +13830,8 @@
       <c r="F159">
         <v>0</v>
       </c>
-      <c r="G159">
-        <v>52.3</v>
+      <c r="G159" s="3">
+        <v>1</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -13927,13 +13893,13 @@
     </row>
     <row r="160" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="B160" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D160" t="s">
         <v>29</v>
@@ -13944,8 +13910,8 @@
       <c r="F160">
         <v>0</v>
       </c>
-      <c r="G160">
-        <v>59.3</v>
+      <c r="G160" s="3">
+        <v>37</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -14007,13 +13973,13 @@
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="B161" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C161" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D161" t="s">
         <v>29</v>
@@ -14024,8 +13990,8 @@
       <c r="F161">
         <v>0</v>
       </c>
-      <c r="G161">
-        <v>84</v>
+      <c r="G161" s="3">
+        <v>32</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -14087,13 +14053,13 @@
     </row>
     <row r="162" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>186</v>
+        <v>1186</v>
       </c>
       <c r="B162" t="s">
-        <v>113</v>
+        <v>205</v>
       </c>
       <c r="C162" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D162" t="s">
         <v>29</v>
@@ -14104,8 +14070,8 @@
       <c r="F162">
         <v>0</v>
       </c>
-      <c r="G162">
-        <v>15.8</v>
+      <c r="G162" s="3">
+        <v>31</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -14167,13 +14133,13 @@
     </row>
     <row r="163" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B163" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C163" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D163" t="s">
         <v>29</v>
@@ -14184,8 +14150,8 @@
       <c r="F163">
         <v>0</v>
       </c>
-      <c r="G163">
-        <v>19.8</v>
+      <c r="G163" s="3">
+        <v>30</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -14247,13 +14213,13 @@
     </row>
     <row r="164" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="B164" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C164" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D164" t="s">
         <v>29</v>
@@ -14264,8 +14230,8 @@
       <c r="F164">
         <v>0</v>
       </c>
-      <c r="G164">
-        <v>21.1</v>
+      <c r="G164" s="3">
+        <v>26</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -14327,13 +14293,13 @@
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>1190</v>
+        <v>1440</v>
       </c>
       <c r="B165" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C165" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D165" t="s">
         <v>29</v>
@@ -14344,8 +14310,8 @@
       <c r="F165">
         <v>0</v>
       </c>
-      <c r="G165">
-        <v>24.2</v>
+      <c r="G165" s="3">
+        <v>14</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -14407,13 +14373,13 @@
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>1184</v>
+        <v>1439</v>
       </c>
       <c r="B166" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C166" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D166" t="s">
         <v>29</v>
@@ -14424,8 +14390,8 @@
       <c r="F166">
         <v>0</v>
       </c>
-      <c r="G166">
-        <v>29</v>
+      <c r="G166" s="3">
+        <v>4</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -14487,10 +14453,10 @@
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B167" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C167" t="s">
         <v>241</v>
@@ -14504,8 +14470,8 @@
       <c r="F167">
         <v>0</v>
       </c>
-      <c r="G167">
-        <v>43.2</v>
+      <c r="G167" s="3">
+        <v>53</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -14567,10 +14533,10 @@
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>1199</v>
+        <v>116</v>
       </c>
       <c r="B168" t="s">
-        <v>212</v>
+        <v>90</v>
       </c>
       <c r="C168" t="s">
         <v>241</v>
@@ -14584,8 +14550,8 @@
       <c r="F168">
         <v>0</v>
       </c>
-      <c r="G168">
-        <v>44.6</v>
+      <c r="G168" s="3">
+        <v>47</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -14647,10 +14613,10 @@
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>116</v>
+        <v>1199</v>
       </c>
       <c r="B169" t="s">
-        <v>90</v>
+        <v>212</v>
       </c>
       <c r="C169" t="s">
         <v>241</v>
@@ -14664,8 +14630,8 @@
       <c r="F169">
         <v>0</v>
       </c>
-      <c r="G169">
-        <v>50.2</v>
+      <c r="G169" s="3">
+        <v>42</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -14727,10 +14693,10 @@
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B170" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C170" t="s">
         <v>241</v>
@@ -14744,8 +14710,8 @@
       <c r="F170">
         <v>0</v>
       </c>
-      <c r="G170">
-        <v>50.6</v>
+      <c r="G170" s="3">
+        <v>49</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -14807,13 +14773,13 @@
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>1439</v>
+        <v>1184</v>
       </c>
       <c r="B171" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C171" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D171" t="s">
         <v>29</v>
@@ -14824,8 +14790,8 @@
       <c r="F171">
         <v>0</v>
       </c>
-      <c r="G171">
-        <v>4</v>
+      <c r="G171" s="3">
+        <v>30</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -14887,13 +14853,13 @@
     </row>
     <row r="172" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>1440</v>
+        <v>1190</v>
       </c>
       <c r="B172" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C172" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D172" t="s">
         <v>29</v>
@@ -14904,8 +14870,8 @@
       <c r="F172">
         <v>0</v>
       </c>
-      <c r="G172">
-        <v>14</v>
+      <c r="G172" s="3">
+        <v>25</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -14967,13 +14933,13 @@
     </row>
     <row r="173" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="B173" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C173" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D173" t="s">
         <v>29</v>
@@ -14984,8 +14950,8 @@
       <c r="F173">
         <v>0</v>
       </c>
-      <c r="G173">
-        <v>25.7</v>
+      <c r="G173" s="3">
+        <v>26</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -15047,13 +15013,13 @@
     </row>
     <row r="174" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A174">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B174" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C174" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D174" t="s">
         <v>29</v>
@@ -15064,8 +15030,8 @@
       <c r="F174">
         <v>0</v>
       </c>
-      <c r="G174">
-        <v>29</v>
+      <c r="G174" s="3">
+        <v>40</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -15127,13 +15093,13 @@
     </row>
     <row r="175" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="B175" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C175" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D175" t="s">
         <v>29</v>
@@ -15144,8 +15110,8 @@
       <c r="F175">
         <v>0</v>
       </c>
-      <c r="G175">
-        <v>30</v>
+      <c r="G175" s="3">
+        <v>21</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -15207,13 +15173,13 @@
     </row>
     <row r="176" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A176">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="B176" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C176" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D176" t="s">
         <v>29</v>
@@ -15224,8 +15190,8 @@
       <c r="F176">
         <v>0</v>
       </c>
-      <c r="G176">
-        <v>30.8</v>
+      <c r="G176" s="3">
+        <v>28</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -15287,13 +15253,13 @@
     </row>
     <row r="177" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A177">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B177" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C177" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D177" t="s">
         <v>29</v>
@@ -15304,8 +15270,8 @@
       <c r="F177">
         <v>0</v>
       </c>
-      <c r="G177">
-        <v>35.700000000000003</v>
+      <c r="G177" s="3">
+        <v>87</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -15367,13 +15333,13 @@
     </row>
     <row r="178" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A178">
-        <v>1196</v>
+        <v>173</v>
       </c>
       <c r="B178" t="s">
-        <v>210</v>
+        <v>107</v>
       </c>
       <c r="C178" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
@@ -15384,8 +15350,8 @@
       <c r="F178">
         <v>0</v>
       </c>
-      <c r="G178">
-        <v>1</v>
+      <c r="G178" s="3">
+        <v>49</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -15447,13 +15413,13 @@
     </row>
     <row r="179" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A179">
-        <v>1198</v>
+        <v>3</v>
       </c>
       <c r="B179" t="s">
-        <v>211</v>
+        <v>28</v>
       </c>
       <c r="C179" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -15464,8 +15430,8 @@
       <c r="F179">
         <v>0</v>
       </c>
-      <c r="G179">
-        <v>1</v>
+      <c r="G179" s="3">
+        <v>80</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -15527,13 +15493,13 @@
     </row>
     <row r="180" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A180">
-        <v>67</v>
+        <v>1441</v>
       </c>
       <c r="B180" t="s">
-        <v>65</v>
+        <v>227</v>
       </c>
       <c r="C180" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -15544,8 +15510,8 @@
       <c r="F180">
         <v>0</v>
       </c>
-      <c r="G180">
-        <v>37.200000000000003</v>
+      <c r="G180" s="3">
+        <v>48</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -15624,8 +15590,8 @@
       <c r="F181">
         <v>0</v>
       </c>
-      <c r="G181">
-        <v>22.5</v>
+      <c r="G181" s="3">
+        <v>24</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -15687,13 +15653,13 @@
     </row>
     <row r="182" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A182">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="B182" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C182" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
@@ -15704,8 +15670,8 @@
       <c r="F182">
         <v>0</v>
       </c>
-      <c r="G182">
-        <v>19.600000000000001</v>
+      <c r="G182" s="3">
+        <v>16</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -15767,13 +15733,13 @@
     </row>
     <row r="183" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A183">
-        <v>1460</v>
+        <v>70</v>
       </c>
       <c r="B183" t="s">
-        <v>233</v>
+        <v>68</v>
       </c>
       <c r="C183" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D183" t="s">
         <v>36</v>
@@ -15784,8 +15750,8 @@
       <c r="F183">
         <v>0</v>
       </c>
-      <c r="G183">
-        <v>11.3</v>
+      <c r="G183" s="3">
+        <v>27</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -15847,13 +15813,13 @@
     </row>
     <row r="184" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A184">
-        <v>1459</v>
+        <v>1367</v>
       </c>
       <c r="B184" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C184" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D184" t="s">
         <v>36</v>
@@ -15864,8 +15830,8 @@
       <c r="F184">
         <v>0</v>
       </c>
-      <c r="G184">
-        <v>12.6</v>
+      <c r="G184" s="3">
+        <v>1</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -15927,13 +15893,13 @@
     </row>
     <row r="185" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A185">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="B185" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C185" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D185" t="s">
         <v>36</v>
@@ -15944,8 +15910,8 @@
       <c r="F185">
         <v>0</v>
       </c>
-      <c r="G185">
-        <v>18.100000000000001</v>
+      <c r="G185" s="3">
+        <v>1</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -16007,13 +15973,13 @@
     </row>
     <row r="186" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>1364</v>
+        <v>183</v>
       </c>
       <c r="B186" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="C186" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D186" t="s">
         <v>36</v>
@@ -16024,8 +15990,8 @@
       <c r="F186">
         <v>0</v>
       </c>
-      <c r="G186">
-        <v>23.3</v>
+      <c r="G186" s="3">
+        <v>24</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -16087,13 +16053,13 @@
     </row>
     <row r="187" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B187" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C187" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D187" t="s">
         <v>36</v>
@@ -16104,8 +16070,8 @@
       <c r="F187">
         <v>0</v>
       </c>
-      <c r="G187">
-        <v>32.4</v>
+      <c r="G187" s="3">
+        <v>22</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -16167,13 +16133,13 @@
     </row>
     <row r="188" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A188">
+        <v>74</v>
+      </c>
+      <c r="B188" t="s">
         <v>72</v>
       </c>
-      <c r="B188" t="s">
-        <v>70</v>
-      </c>
       <c r="C188" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D188" t="s">
         <v>36</v>
@@ -16184,8 +16150,8 @@
       <c r="F188">
         <v>0</v>
       </c>
-      <c r="G188">
-        <v>44.3</v>
+      <c r="G188" s="3">
+        <v>21</v>
       </c>
       <c r="H188">
         <v>0</v>
@@ -16247,13 +16213,13 @@
     </row>
     <row r="189" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="B189" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C189" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D189" t="s">
         <v>36</v>
@@ -16264,8 +16230,8 @@
       <c r="F189">
         <v>0</v>
       </c>
-      <c r="G189">
-        <v>10.3</v>
+      <c r="G189" s="3">
+        <v>18</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -16327,13 +16293,13 @@
     </row>
     <row r="190" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>1356</v>
+        <v>179</v>
       </c>
       <c r="B190" t="s">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="C190" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D190" t="s">
         <v>36</v>
@@ -16344,8 +16310,8 @@
       <c r="F190">
         <v>0</v>
       </c>
-      <c r="G190">
-        <v>13.1</v>
+      <c r="G190" s="3">
+        <v>18</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -16407,13 +16373,13 @@
     </row>
     <row r="191" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>73</v>
+        <v>1358</v>
       </c>
       <c r="B191" t="s">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="C191" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D191" t="s">
         <v>36</v>
@@ -16424,8 +16390,8 @@
       <c r="F191">
         <v>0</v>
       </c>
-      <c r="G191">
-        <v>16.7</v>
+      <c r="G191" s="3">
+        <v>15</v>
       </c>
       <c r="H191">
         <v>0</v>
@@ -16487,13 +16453,13 @@
     </row>
     <row r="192" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A192">
-        <v>1354</v>
+        <v>1363</v>
       </c>
       <c r="B192" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C192" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D192" t="s">
         <v>36</v>
@@ -16504,8 +16470,8 @@
       <c r="F192">
         <v>0</v>
       </c>
-      <c r="G192">
-        <v>16.8</v>
+      <c r="G192" s="3">
+        <v>14</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -16567,13 +16533,13 @@
     </row>
     <row r="193" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="B193" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C193" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D193" t="s">
         <v>36</v>
@@ -16584,8 +16550,8 @@
       <c r="F193">
         <v>0</v>
       </c>
-      <c r="G193">
-        <v>17.2</v>
+      <c r="G193" s="3">
+        <v>18</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -16647,13 +16613,13 @@
     </row>
     <row r="194" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A194">
-        <v>1355</v>
+        <v>1524</v>
       </c>
       <c r="B194" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C194" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D194" t="s">
         <v>36</v>
@@ -16664,8 +16630,8 @@
       <c r="F194">
         <v>0</v>
       </c>
-      <c r="G194">
-        <v>19.8</v>
+      <c r="G194" s="3">
+        <v>11</v>
       </c>
       <c r="H194">
         <v>0</v>
@@ -16727,10 +16693,10 @@
     </row>
     <row r="195" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>1353</v>
+        <v>69</v>
       </c>
       <c r="B195" t="s">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="C195" t="s">
         <v>241</v>
@@ -16744,8 +16710,8 @@
       <c r="F195">
         <v>0</v>
       </c>
-      <c r="G195">
-        <v>25.2</v>
+      <c r="G195" s="3">
+        <v>36</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -16807,10 +16773,10 @@
     </row>
     <row r="196" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A196">
-        <v>69</v>
+        <v>1353</v>
       </c>
       <c r="B196" t="s">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="C196" t="s">
         <v>241</v>
@@ -16824,8 +16790,8 @@
       <c r="F196">
         <v>0</v>
       </c>
-      <c r="G196">
-        <v>28.8</v>
+      <c r="G196" s="3">
+        <v>26</v>
       </c>
       <c r="H196">
         <v>0</v>
@@ -16887,13 +16853,13 @@
     </row>
     <row r="197" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A197">
-        <v>1524</v>
+        <v>1355</v>
       </c>
       <c r="B197" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="C197" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D197" t="s">
         <v>36</v>
@@ -16904,8 +16870,8 @@
       <c r="F197">
         <v>0</v>
       </c>
-      <c r="G197">
-        <v>6.2</v>
+      <c r="G197" s="3">
+        <v>21</v>
       </c>
       <c r="H197">
         <v>0</v>
@@ -16967,13 +16933,13 @@
     </row>
     <row r="198" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A198">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="B198" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C198" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D198" t="s">
         <v>36</v>
@@ -16984,8 +16950,8 @@
       <c r="F198">
         <v>0</v>
       </c>
-      <c r="G198">
-        <v>6.7</v>
+      <c r="G198" s="3">
+        <v>24</v>
       </c>
       <c r="H198">
         <v>0</v>
@@ -17047,13 +17013,13 @@
     </row>
     <row r="199" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A199">
-        <v>1363</v>
+        <v>1354</v>
       </c>
       <c r="B199" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C199" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D199" t="s">
         <v>36</v>
@@ -17064,8 +17030,8 @@
       <c r="F199">
         <v>0</v>
       </c>
-      <c r="G199">
-        <v>9.6</v>
+      <c r="G199" s="3">
+        <v>17</v>
       </c>
       <c r="H199">
         <v>0</v>
@@ -17127,13 +17093,13 @@
     </row>
     <row r="200" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A200">
-        <v>1358</v>
+        <v>73</v>
       </c>
       <c r="B200" t="s">
-        <v>218</v>
+        <v>71</v>
       </c>
       <c r="C200" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D200" t="s">
         <v>36</v>
@@ -17144,8 +17110,8 @@
       <c r="F200">
         <v>0</v>
       </c>
-      <c r="G200">
-        <v>10.8</v>
+      <c r="G200" s="3">
+        <v>17</v>
       </c>
       <c r="H200">
         <v>0</v>
@@ -17207,13 +17173,13 @@
     </row>
     <row r="201" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A201">
-        <v>179</v>
+        <v>1356</v>
       </c>
       <c r="B201" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="C201" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D201" t="s">
         <v>36</v>
@@ -17224,8 +17190,8 @@
       <c r="F201">
         <v>0</v>
       </c>
-      <c r="G201">
-        <v>12.3</v>
+      <c r="G201" s="3">
+        <v>13</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -17287,13 +17253,13 @@
     </row>
     <row r="202" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A202">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="B202" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C202" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D202" t="s">
         <v>36</v>
@@ -17304,8 +17270,8 @@
       <c r="F202">
         <v>0</v>
       </c>
-      <c r="G202">
-        <v>13</v>
+      <c r="G202" s="3">
+        <v>10</v>
       </c>
       <c r="H202">
         <v>0</v>
@@ -17367,13 +17333,13 @@
     </row>
     <row r="203" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A203">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B203" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C203" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D203" t="s">
         <v>36</v>
@@ -17384,8 +17350,8 @@
       <c r="F203">
         <v>0</v>
       </c>
-      <c r="G203">
-        <v>15.2</v>
+      <c r="G203" s="3">
+        <v>48</v>
       </c>
       <c r="H203">
         <v>0</v>
@@ -17447,13 +17413,13 @@
     </row>
     <row r="204" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A204">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B204" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C204" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D204" t="s">
         <v>36</v>
@@ -17464,8 +17430,8 @@
       <c r="F204">
         <v>0</v>
       </c>
-      <c r="G204">
-        <v>16.2</v>
+      <c r="G204" s="3">
+        <v>53</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -17527,13 +17493,13 @@
     </row>
     <row r="205" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A205">
-        <v>183</v>
+        <v>1364</v>
       </c>
       <c r="B205" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
       <c r="C205" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D205" t="s">
         <v>36</v>
@@ -17544,8 +17510,8 @@
       <c r="F205">
         <v>0</v>
       </c>
-      <c r="G205">
-        <v>17.3</v>
+      <c r="G205" s="3">
+        <v>27</v>
       </c>
       <c r="H205">
         <v>0</v>
@@ -17607,13 +17573,13 @@
     </row>
     <row r="206" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A206">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B206" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C206" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D206" t="s">
         <v>36</v>
@@ -17624,8 +17590,8 @@
       <c r="F206">
         <v>0</v>
       </c>
-      <c r="G206">
-        <v>1</v>
+      <c r="G206" s="3">
+        <v>25</v>
       </c>
       <c r="H206">
         <v>0</v>
@@ -17687,13 +17653,13 @@
     </row>
     <row r="207" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A207">
-        <v>1369</v>
+        <v>1459</v>
       </c>
       <c r="B207" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C207" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D207" t="s">
         <v>36</v>
@@ -17704,8 +17670,8 @@
       <c r="F207">
         <v>0</v>
       </c>
-      <c r="G207">
-        <v>1</v>
+      <c r="G207" s="3">
+        <v>18</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -17767,13 +17733,13 @@
     </row>
     <row r="208" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A208">
-        <v>70</v>
+        <v>1460</v>
       </c>
       <c r="B208" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="C208" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D208" t="s">
         <v>36</v>
@@ -17784,8 +17750,8 @@
       <c r="F208">
         <v>0</v>
       </c>
-      <c r="G208">
-        <v>18.2</v>
+      <c r="G208" s="3">
+        <v>17</v>
       </c>
       <c r="H208">
         <v>0</v>
@@ -17846,6 +17812,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH209">
+    <sortCondition ref="D2:D209"/>
+    <sortCondition descending="1" ref="C2:C209"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
